--- a/docs/time-logs/MartinChi_I1_Timesheet.xlsx
+++ b/docs/time-logs/MartinChi_I1_Timesheet.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Chi Martin</t>
   </si>
   <si>
-    <t xml:space="preserve">Iteration 1</t>
+    <t xml:space="preserve">Iteration 2</t>
   </si>
   <si>
     <t xml:space="preserve">DATES</t>
@@ -73,7 +73,7 @@
     <numFmt numFmtId="165" formatCode="d\-mmm"/>
     <numFmt numFmtId="166" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -117,12 +117,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -200,7 +194,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -254,10 +248,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -739,7 +729,7 @@
       <c r="B6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="9"/>
@@ -801,18 +791,18 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -829,18 +819,18 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -857,18 +847,18 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -885,18 +875,18 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="13"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -913,18 +903,18 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -941,18 +931,18 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="13"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -969,18 +959,18 @@
       <c r="Z13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -997,23 +987,23 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="27" t="n">
         <f aca="false">SUM(B4:B14)</f>
         <v>7</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
